--- a/storage/assets/webc_excel/WEBC IDEAL MOTOR.xlsx
+++ b/storage/assets/webc_excel/WEBC IDEAL MOTOR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\h720s-itts01\H720_TS03_ARTEAMFS\KPB\PORTAL\WEBC MD START FROM AGUSTUS 2022\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F588E2F6-AA07-4313-97E0-E10BF7526DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B9DCF7-F06F-4116-A60D-6874178D7FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4127" uniqueCount="1846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4741" uniqueCount="2021">
   <si>
     <t>nama_region</t>
   </si>
@@ -5564,6 +5564,531 @@
   </si>
   <si>
     <t>JMA118TK227977</t>
+  </si>
+  <si>
+    <t>00728-PKB-2610981</t>
+  </si>
+  <si>
+    <t>79af4307-2ea1-459b-1789-08def1bafa1e</t>
+  </si>
+  <si>
+    <t>JMJ1E1110191</t>
+  </si>
+  <si>
+    <t>KB2833SAM</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21214476520260804132340HVOUMA.jpg</t>
+  </si>
+  <si>
+    <t>JMJ119TK110165</t>
+  </si>
+  <si>
+    <t>00728-PKB-2610980</t>
+  </si>
+  <si>
+    <t>6633759c-7646-477a-4049-08def1ba6f81</t>
+  </si>
+  <si>
+    <t>JMH1E1447645</t>
+  </si>
+  <si>
+    <t>KB2613AAC</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21214476520260804131159K64ES3.jpg</t>
+  </si>
+  <si>
+    <t>JMH110TK449423</t>
+  </si>
+  <si>
+    <t>00728-PKB-2611162</t>
+  </si>
+  <si>
+    <t>18214200-d3bd-4558-dbcc-08def3458594</t>
+  </si>
+  <si>
+    <t>JMF2E1498723</t>
+  </si>
+  <si>
+    <t>KB3405SAI</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21460073220260807111954B6WJ19.jpg</t>
+  </si>
+  <si>
+    <t>JMF219SK499769</t>
+  </si>
+  <si>
+    <t>00728-PKB-2611923</t>
+  </si>
+  <si>
+    <t>f30a81b1-2b51-48e7-d795-08def8cdc9d1</t>
+  </si>
+  <si>
+    <t>Via</t>
+  </si>
+  <si>
+    <t>089672829978</t>
+  </si>
+  <si>
+    <t>REVO X</t>
+  </si>
+  <si>
+    <t>JBK3E1618265</t>
+  </si>
+  <si>
+    <t>KB6875XQ</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/216033450202608150933342UL3RT.jpg</t>
+  </si>
+  <si>
+    <t>JBK317SK620148</t>
+  </si>
+  <si>
+    <t>00728-PKB-2611527</t>
+  </si>
+  <si>
+    <t>5b53976c-50ab-45cc-cb98-08def8cdc9d1</t>
+  </si>
+  <si>
+    <t>JMH2E1843258</t>
+  </si>
+  <si>
+    <t>KB4669AAB</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21603345020260813093024KPYUHW.jpg</t>
+  </si>
+  <si>
+    <t>JMH219TK846952</t>
+  </si>
+  <si>
+    <t>00728-PKB-2611408</t>
+  </si>
+  <si>
+    <t>4b8bf6c0-463c-40a9-84b8-08def7f39631</t>
+  </si>
+  <si>
+    <t>KF01E2052996</t>
+  </si>
+  <si>
+    <t>KB2188AAB</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21603345020260812102323C1UEAE.jpg</t>
+  </si>
+  <si>
+    <t>KF0124TK053200</t>
+  </si>
+  <si>
+    <t>00728-PKB-2612905</t>
+  </si>
+  <si>
+    <t>f033b6c4-6cbe-4626-60bd-08df09ccc70e</t>
+  </si>
+  <si>
+    <t>JMH2E1915572</t>
+  </si>
+  <si>
+    <t>KB4159SAM</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21347004720260905160323EQ0AXG.heic</t>
+  </si>
+  <si>
+    <t>JMH218TK916277</t>
+  </si>
+  <si>
+    <t>00728-PKB-2612904</t>
+  </si>
+  <si>
+    <t>106393c5-7488-4573-af9c-08df09c9f8cd</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/213470047202609051516474NXQIM.heic</t>
+  </si>
+  <si>
+    <t>00728-PKB-2612903</t>
+  </si>
+  <si>
+    <t>3dbb4f94-caa4-43ac-7939-08df09c9936d</t>
+  </si>
+  <si>
+    <t>STYLO 160 ABS</t>
+  </si>
+  <si>
+    <t>KFD1E1331750</t>
+  </si>
+  <si>
+    <t>KB2935AAC</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21347004720260905143307HWGRVO.jpg</t>
+  </si>
+  <si>
+    <t>KFD110TK331752</t>
+  </si>
+  <si>
+    <t>00728-PKB-2612902</t>
+  </si>
+  <si>
+    <t>ee69d5ca-cc07-4f88-ecef-08df09ca47dd</t>
+  </si>
+  <si>
+    <t>SCOOPY FI PRESTIGE</t>
+  </si>
+  <si>
+    <t>JMH2E1946062</t>
+  </si>
+  <si>
+    <t>KB3188SAM</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21347004720260905130017O45NHT.heic</t>
+  </si>
+  <si>
+    <t>JMH218TK946489</t>
+  </si>
+  <si>
+    <t>00728-PKB-2612726</t>
+  </si>
+  <si>
+    <t>c8f4d049-95e0-40dc-114c-08df07b3d03e</t>
+  </si>
+  <si>
+    <t>BEAT SPORTY DLX SMART KEY</t>
+  </si>
+  <si>
+    <t>JMF2E1605488</t>
+  </si>
+  <si>
+    <t>KB5253AAB</t>
+  </si>
+  <si>
+    <t>2026-05-09</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21347004720260902092117OJPAXR.jpg</t>
+  </si>
+  <si>
+    <t>JMF211SK605406</t>
+  </si>
+  <si>
+    <t>00728-PKB-2613052</t>
+  </si>
+  <si>
+    <t>34e625dc-23c5-4f05-4c0f-08df0cb2584c</t>
+  </si>
+  <si>
+    <t>KFE1E1561938</t>
+  </si>
+  <si>
+    <t>KB3187SAM</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21347004720260908153406YMK7JN.heic</t>
+  </si>
+  <si>
+    <t>KFE112TK561783</t>
+  </si>
+  <si>
+    <t>00728-PKB-2613056</t>
+  </si>
+  <si>
+    <t>f9145ca5-6cd9-4caa-742e-08df0e186167</t>
+  </si>
+  <si>
+    <t>KFD1E1340114</t>
+  </si>
+  <si>
+    <t>KB3747AAC</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21460073220260909114104E5I7OE.jpg</t>
+  </si>
+  <si>
+    <t>KFD113TK340610</t>
+  </si>
+  <si>
+    <t>00728-PKB-2613055</t>
+  </si>
+  <si>
+    <t>76b86d97-04c2-4c7b-4fd9-08df0cb2584c</t>
+  </si>
+  <si>
+    <t>JME1E2096123</t>
+  </si>
+  <si>
+    <t>KB2398GAU</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21460073220260909113304VGR8FB.jpg</t>
+  </si>
+  <si>
+    <t>JME128TK100517</t>
+  </si>
+  <si>
+    <t>00728-PKB-2613054</t>
+  </si>
+  <si>
+    <t>7cd40124-ea53-4a65-c3d5-08df09c9f8cd</t>
+  </si>
+  <si>
+    <t>KFD1E1333599</t>
+  </si>
+  <si>
+    <t>KB3287AAC</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/213470047202609091132057MXEIC.jpg</t>
+  </si>
+  <si>
+    <t>KFD116TK333098</t>
+  </si>
+  <si>
+    <t>00728-PKB-2613287</t>
+  </si>
+  <si>
+    <t>c145bece-3403-4be9-bba8-08df0f914d80</t>
+  </si>
+  <si>
+    <t>KFA1E1327465</t>
+  </si>
+  <si>
+    <t>KB4106SAI</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21347004720260912124946BNT8KP.jpg</t>
+  </si>
+  <si>
+    <t>KFA117SK326657</t>
+  </si>
+  <si>
+    <t>00728-PKB-2613286</t>
+  </si>
+  <si>
+    <t>e0d8a138-a9fd-4d38-bb83-08df0f914d80</t>
+  </si>
+  <si>
+    <t>JMA1E1240373</t>
+  </si>
+  <si>
+    <t>KB3176AAC</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21347004720260912124028KMYT2G.jpg</t>
+  </si>
+  <si>
+    <t>JMA112TK242295</t>
+  </si>
+  <si>
+    <t>00728-PKB-2613271</t>
+  </si>
+  <si>
+    <t>dabf6eb3-72a6-4a2f-73ce-08df0f8fbffb</t>
+  </si>
+  <si>
+    <t>JMF1E1425539</t>
+  </si>
+  <si>
+    <t>KB3041AAC</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/213470047202609111159149OIAVY.jpg</t>
+  </si>
+  <si>
+    <t>JMF116TK426555</t>
+  </si>
+  <si>
+    <t>00728-PKB-2613270</t>
+  </si>
+  <si>
+    <t>f7b7a8a4-d904-4ba9-e35d-08df0f926d37</t>
+  </si>
+  <si>
+    <t>JMF1E1437800</t>
+  </si>
+  <si>
+    <t>KB2476MAP</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21347004720260911115142L51BNS.heic</t>
+  </si>
+  <si>
+    <t>JMF115TK438695</t>
+  </si>
+  <si>
+    <t>00728-PKB-2613269</t>
+  </si>
+  <si>
+    <t>532d5424-344d-4673-73bf-08df0f8fbffb</t>
+  </si>
+  <si>
+    <t>JMB1E1255644</t>
+  </si>
+  <si>
+    <t>KB3502MAP</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21347004720260911114715YCFQPP.heic</t>
+  </si>
+  <si>
+    <t>JMB117TK256053</t>
+  </si>
+  <si>
+    <t>00728-PKB-2613268</t>
+  </si>
+  <si>
+    <t>badcea50-367e-420f-2ad7-08df0f9043b0</t>
+  </si>
+  <si>
+    <t>Vario 125 CBS ISS eSP</t>
+  </si>
+  <si>
+    <t>JMK1E1226301</t>
+  </si>
+  <si>
+    <t>KB3755AAC</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21460073220260911114055N9L5IE.jpg</t>
+  </si>
+  <si>
+    <t>JMK111TK226580</t>
+  </si>
+  <si>
+    <t>00728-PKB-2613439</t>
+  </si>
+  <si>
+    <t>7834a016-e426-4082-40c8-08df0f9043b0</t>
+  </si>
+  <si>
+    <t>JMH1E1452945</t>
+  </si>
+  <si>
+    <t>KB6265SAK</t>
+  </si>
+  <si>
+    <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21347004720260915110633XT6ZDY.heic</t>
+  </si>
+  <si>
+    <t>JMH110TK454721</t>
+  </si>
+  <si>
+    <t>00728-PKB-2613438</t>
+  </si>
+  <si>
+    <t>d3cd327a-4f93-46cb-33ca-08df123189fe</t>
+  </si>
+  <si>
+    <t>JBP1E2170597</t>
+  </si>
+  <si>
+    <t>KB3404AAC</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/21347004720260915105850YI8VQO.jpg</t>
+  </si>
+  <si>
+    <t>JBP123TK170993</t>
+  </si>
+  <si>
+    <t>00728-PKB-2613890</t>
+  </si>
+  <si>
+    <t>164927de-bfd1-4135-1ed8-08df18a44c02</t>
+  </si>
+  <si>
+    <t>JMC1E1721867</t>
+  </si>
+  <si>
+    <t>KB6491XJ</t>
+  </si>
+  <si>
+    <t>2025-09-20</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>https://hana.modakita.com/azd942/avatar/kpb/2-01M38VNSZT7A0Y5JN0XAGFS2BR-eda32.jpg</t>
+  </si>
+  <si>
+    <t>JMC117SK723041</t>
+  </si>
+  <si>
+    <t>No. Voucher</t>
   </si>
 </sst>
 </file>
@@ -5613,10 +6138,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5966,7 +6492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R253"/>
+  <dimension ref="A1:S279"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="14" max="14" width="11" customWidth="1"/>
@@ -18750,787 +19276,2246 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="2" t="s">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
         <v>0</v>
       </c>
-      <c r="B240" s="2" t="s">
+      <c r="B240" t="s">
         <v>1</v>
       </c>
-      <c r="C240" s="2" t="s">
+      <c r="C240" t="s">
         <v>2</v>
       </c>
-      <c r="D240" s="2" t="s">
+      <c r="D240" t="s">
         <v>3</v>
       </c>
-      <c r="E240" s="2" t="s">
+      <c r="E240" t="s">
         <v>4</v>
       </c>
-      <c r="F240" s="2" t="s">
+      <c r="F240" t="s">
         <v>5</v>
       </c>
-      <c r="G240" s="2" t="s">
+      <c r="G240" t="s">
         <v>6</v>
       </c>
-      <c r="H240" s="2" t="s">
+      <c r="H240" t="s">
         <v>7</v>
       </c>
-      <c r="I240" s="2" t="s">
+      <c r="I240" t="s">
         <v>8</v>
       </c>
-      <c r="J240" s="2" t="s">
+      <c r="J240" t="s">
         <v>9</v>
       </c>
-      <c r="K240" s="2" t="s">
+      <c r="K240" t="s">
         <v>10</v>
       </c>
-      <c r="L240" s="2" t="s">
+      <c r="L240" t="s">
         <v>11</v>
       </c>
-      <c r="M240" s="2" t="s">
+      <c r="M240" t="s">
         <v>12</v>
       </c>
-      <c r="N240" s="2" t="s">
+      <c r="N240" t="s">
         <v>13</v>
       </c>
-      <c r="O240" s="2" t="s">
+      <c r="O240" t="s">
         <v>14</v>
       </c>
-      <c r="P240" s="2" t="s">
+      <c r="P240" t="s">
         <v>15</v>
       </c>
-      <c r="Q240" s="2" t="s">
+      <c r="Q240" t="s">
         <v>16</v>
       </c>
-      <c r="R240" s="2" t="s">
+      <c r="R240" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="241" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B241" s="2" t="s">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>17</v>
+      </c>
+      <c r="B241" t="s">
         <v>1753</v>
       </c>
-      <c r="C241" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D241" s="2" t="s">
+      <c r="C241" t="s">
+        <v>19</v>
+      </c>
+      <c r="D241" t="s">
         <v>1754</v>
       </c>
-      <c r="E241" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F241" s="2" t="s">
+      <c r="E241" t="s">
+        <v>21</v>
+      </c>
+      <c r="F241" t="s">
         <v>1182</v>
       </c>
-      <c r="G241" s="2" t="s">
+      <c r="G241" t="s">
         <v>1183</v>
       </c>
-      <c r="H241" s="2" t="s">
+      <c r="H241" t="s">
         <v>1572</v>
       </c>
-      <c r="I241" s="2" t="s">
+      <c r="I241" t="s">
         <v>1755</v>
       </c>
-      <c r="J241" s="2" t="s">
+      <c r="J241" t="s">
         <v>1756</v>
       </c>
-      <c r="K241" s="2" t="s">
+      <c r="K241" t="s">
         <v>27</v>
       </c>
-      <c r="L241" s="2">
+      <c r="L241">
         <v>876</v>
       </c>
-      <c r="M241" s="2" t="s">
+      <c r="M241" t="s">
         <v>1757</v>
       </c>
-      <c r="N241" s="2" t="s">
+      <c r="N241" t="s">
         <v>1758</v>
       </c>
-      <c r="O241" s="2" t="s">
+      <c r="O241" t="s">
         <v>1759</v>
       </c>
-      <c r="P241" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q241" s="2" t="s">
+      <c r="P241" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q241" t="s">
         <v>1760</v>
       </c>
-      <c r="R241" s="2">
+      <c r="R241">
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B242" s="2" t="s">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>17</v>
+      </c>
+      <c r="B242" t="s">
         <v>1761</v>
       </c>
-      <c r="C242" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D242" s="2" t="s">
+      <c r="C242" t="s">
+        <v>19</v>
+      </c>
+      <c r="D242" t="s">
         <v>1762</v>
       </c>
-      <c r="E242" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F242" s="2" t="s">
+      <c r="E242" t="s">
+        <v>21</v>
+      </c>
+      <c r="F242" t="s">
         <v>970</v>
       </c>
-      <c r="G242" s="2" t="s">
+      <c r="G242" t="s">
         <v>971</v>
       </c>
-      <c r="H242" s="2" t="s">
+      <c r="H242" t="s">
         <v>55</v>
       </c>
-      <c r="I242" s="2" t="s">
+      <c r="I242" t="s">
         <v>1763</v>
       </c>
-      <c r="J242" s="2" t="s">
+      <c r="J242" t="s">
         <v>1764</v>
       </c>
-      <c r="K242" s="2" t="s">
+      <c r="K242" t="s">
         <v>27</v>
       </c>
-      <c r="L242" s="2">
+      <c r="L242">
         <v>398</v>
       </c>
-      <c r="M242" s="2" t="s">
+      <c r="M242" t="s">
         <v>1765</v>
       </c>
-      <c r="N242" s="2" t="s">
+      <c r="N242" t="s">
         <v>1766</v>
       </c>
-      <c r="O242" s="2" t="s">
+      <c r="O242" t="s">
         <v>1767</v>
       </c>
-      <c r="P242" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q242" s="2" t="s">
+      <c r="P242" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q242" t="s">
         <v>1768</v>
       </c>
-      <c r="R242" s="2">
+      <c r="R242">
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B243" s="2" t="s">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>17</v>
+      </c>
+      <c r="B243" t="s">
         <v>1769</v>
       </c>
-      <c r="C243" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D243" s="2" t="s">
+      <c r="C243" t="s">
+        <v>19</v>
+      </c>
+      <c r="D243" t="s">
         <v>1770</v>
       </c>
-      <c r="E243" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F243" s="2" t="s">
+      <c r="E243" t="s">
+        <v>21</v>
+      </c>
+      <c r="F243" t="s">
         <v>1182</v>
       </c>
-      <c r="G243" s="2" t="s">
+      <c r="G243" t="s">
         <v>1183</v>
       </c>
-      <c r="H243" s="2" t="s">
+      <c r="H243" t="s">
         <v>1184</v>
       </c>
-      <c r="I243" s="2" t="s">
+      <c r="I243" t="s">
         <v>1771</v>
       </c>
-      <c r="J243" s="2" t="s">
+      <c r="J243" t="s">
         <v>1772</v>
       </c>
-      <c r="K243" s="2" t="s">
+      <c r="K243" t="s">
         <v>58</v>
       </c>
-      <c r="L243" s="2">
+      <c r="L243">
         <v>7089</v>
       </c>
-      <c r="M243" s="2" t="s">
+      <c r="M243" t="s">
         <v>1387</v>
       </c>
-      <c r="N243" s="2" t="s">
+      <c r="N243" t="s">
         <v>1766</v>
       </c>
-      <c r="O243" s="2" t="s">
+      <c r="O243" t="s">
         <v>1773</v>
       </c>
-      <c r="P243" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q243" s="2" t="s">
+      <c r="P243" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q243" t="s">
         <v>1774</v>
       </c>
-      <c r="R243" s="2">
+      <c r="R243">
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B244" s="2" t="s">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>17</v>
+      </c>
+      <c r="B244" t="s">
         <v>1775</v>
       </c>
-      <c r="C244" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D244" s="2" t="s">
+      <c r="C244" t="s">
+        <v>19</v>
+      </c>
+      <c r="D244" t="s">
         <v>1776</v>
       </c>
-      <c r="E244" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F244" s="2" t="s">
+      <c r="E244" t="s">
+        <v>21</v>
+      </c>
+      <c r="F244" t="s">
         <v>970</v>
       </c>
-      <c r="G244" s="2" t="s">
+      <c r="G244" t="s">
         <v>971</v>
       </c>
-      <c r="H244" s="2" t="s">
+      <c r="H244" t="s">
         <v>1777</v>
       </c>
-      <c r="I244" s="2" t="s">
+      <c r="I244" t="s">
         <v>1778</v>
       </c>
-      <c r="J244" s="2" t="s">
+      <c r="J244" t="s">
         <v>1779</v>
       </c>
-      <c r="K244" s="2" t="s">
+      <c r="K244" t="s">
         <v>27</v>
       </c>
-      <c r="L244" s="2">
+      <c r="L244">
         <v>586</v>
       </c>
-      <c r="M244" s="2" t="s">
+      <c r="M244" t="s">
         <v>1780</v>
       </c>
-      <c r="N244" s="2" t="s">
+      <c r="N244" t="s">
         <v>1781</v>
       </c>
-      <c r="O244" s="2" t="s">
+      <c r="O244" t="s">
         <v>1782</v>
       </c>
-      <c r="P244" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q244" s="2" t="s">
+      <c r="P244" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q244" t="s">
         <v>1783</v>
       </c>
-      <c r="R244" s="2">
+      <c r="R244">
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B245" s="2" t="s">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>17</v>
+      </c>
+      <c r="B245" t="s">
         <v>1784</v>
       </c>
-      <c r="C245" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D245" s="2" t="s">
+      <c r="C245" t="s">
+        <v>19</v>
+      </c>
+      <c r="D245" t="s">
         <v>1785</v>
       </c>
-      <c r="E245" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F245" s="2" t="s">
+      <c r="E245" t="s">
+        <v>21</v>
+      </c>
+      <c r="F245" t="s">
         <v>1182</v>
       </c>
-      <c r="G245" s="2" t="s">
+      <c r="G245" t="s">
         <v>1183</v>
       </c>
-      <c r="H245" s="2" t="s">
+      <c r="H245" t="s">
         <v>1786</v>
       </c>
-      <c r="I245" s="2" t="s">
+      <c r="I245" t="s">
         <v>1787</v>
       </c>
-      <c r="J245" s="2" t="s">
+      <c r="J245" t="s">
         <v>1788</v>
       </c>
-      <c r="K245" s="2" t="s">
+      <c r="K245" t="s">
         <v>69</v>
       </c>
-      <c r="L245" s="2">
+      <c r="L245">
         <v>5080</v>
       </c>
-      <c r="M245" s="2" t="s">
+      <c r="M245" t="s">
         <v>1789</v>
       </c>
-      <c r="N245" s="2" t="s">
+      <c r="N245" t="s">
         <v>1781</v>
       </c>
-      <c r="O245" s="2" t="s">
+      <c r="O245" t="s">
         <v>1790</v>
       </c>
-      <c r="P245" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q245" s="2" t="s">
+      <c r="P245" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q245" t="s">
         <v>1791</v>
       </c>
-      <c r="R245" s="2">
+      <c r="R245">
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A246" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B246" s="2" t="s">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>17</v>
+      </c>
+      <c r="B246" t="s">
         <v>1792</v>
       </c>
-      <c r="C246" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D246" s="2" t="s">
+      <c r="C246" t="s">
+        <v>19</v>
+      </c>
+      <c r="D246" t="s">
         <v>1793</v>
       </c>
-      <c r="E246" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F246" s="2" t="s">
+      <c r="E246" t="s">
+        <v>21</v>
+      </c>
+      <c r="F246" t="s">
         <v>1182</v>
       </c>
-      <c r="G246" s="2" t="s">
+      <c r="G246" t="s">
         <v>1183</v>
       </c>
-      <c r="H246" s="2" t="s">
+      <c r="H246" t="s">
         <v>1794</v>
       </c>
-      <c r="I246" s="2" t="s">
+      <c r="I246" t="s">
         <v>1795</v>
       </c>
-      <c r="J246" s="2" t="s">
+      <c r="J246" t="s">
         <v>1796</v>
       </c>
-      <c r="K246" s="2" t="s">
+      <c r="K246" t="s">
         <v>27</v>
       </c>
-      <c r="L246" s="2">
+      <c r="L246">
         <v>976</v>
       </c>
-      <c r="M246" s="2" t="s">
+      <c r="M246" t="s">
         <v>1684</v>
       </c>
-      <c r="N246" s="2" t="s">
+      <c r="N246" t="s">
         <v>1797</v>
       </c>
-      <c r="O246" s="2" t="s">
+      <c r="O246" t="s">
         <v>1798</v>
       </c>
-      <c r="P246" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q246" s="2" t="s">
+      <c r="P246" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q246" t="s">
         <v>1799</v>
       </c>
-      <c r="R246" s="2">
+      <c r="R246">
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="1" t="s">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
         <v>0</v>
       </c>
-      <c r="B247" s="1" t="s">
+      <c r="B247" t="s">
         <v>1</v>
       </c>
-      <c r="C247" s="1" t="s">
+      <c r="C247" t="s">
         <v>2</v>
       </c>
-      <c r="D247" s="1" t="s">
+      <c r="D247" t="s">
         <v>3</v>
       </c>
-      <c r="E247" s="1" t="s">
+      <c r="E247" t="s">
         <v>4</v>
       </c>
-      <c r="F247" s="1" t="s">
+      <c r="F247" t="s">
         <v>5</v>
       </c>
-      <c r="G247" s="1" t="s">
+      <c r="G247" t="s">
         <v>6</v>
       </c>
-      <c r="H247" s="1" t="s">
+      <c r="H247" t="s">
         <v>7</v>
       </c>
-      <c r="I247" s="1" t="s">
+      <c r="I247" t="s">
         <v>8</v>
       </c>
-      <c r="J247" s="1" t="s">
+      <c r="J247" t="s">
         <v>9</v>
       </c>
-      <c r="K247" s="1" t="s">
+      <c r="K247" t="s">
         <v>10</v>
       </c>
-      <c r="L247" s="1" t="s">
+      <c r="L247" t="s">
         <v>11</v>
       </c>
-      <c r="M247" s="1" t="s">
+      <c r="M247" t="s">
         <v>12</v>
       </c>
-      <c r="N247" s="1" t="s">
+      <c r="N247" t="s">
         <v>13</v>
       </c>
-      <c r="O247" s="1" t="s">
+      <c r="O247" t="s">
         <v>14</v>
       </c>
-      <c r="P247" s="1" t="s">
+      <c r="P247" t="s">
         <v>15</v>
       </c>
-      <c r="Q247" s="1" t="s">
+      <c r="Q247" t="s">
         <v>16</v>
       </c>
-      <c r="R247" s="1" t="s">
+      <c r="R247" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="248" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A248" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B248" s="1" t="s">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>17</v>
+      </c>
+      <c r="B248" t="s">
         <v>1800</v>
       </c>
-      <c r="C248" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D248" s="1" t="s">
+      <c r="C248" t="s">
+        <v>19</v>
+      </c>
+      <c r="D248" t="s">
         <v>1801</v>
       </c>
-      <c r="E248" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F248" s="1" t="s">
+      <c r="E248" t="s">
+        <v>21</v>
+      </c>
+      <c r="F248" t="s">
         <v>1182</v>
       </c>
-      <c r="G248" s="1" t="s">
+      <c r="G248" t="s">
         <v>1183</v>
       </c>
-      <c r="H248" s="1" t="s">
+      <c r="H248" t="s">
         <v>1794</v>
       </c>
-      <c r="I248" s="1" t="s">
+      <c r="I248" t="s">
         <v>1802</v>
       </c>
-      <c r="J248" s="1" t="s">
+      <c r="J248" t="s">
         <v>1803</v>
       </c>
-      <c r="K248" s="1" t="s">
+      <c r="K248" t="s">
         <v>69</v>
       </c>
-      <c r="L248" s="1">
+      <c r="L248">
         <v>3407</v>
       </c>
-      <c r="M248" s="1" t="s">
+      <c r="M248" t="s">
         <v>1804</v>
       </c>
-      <c r="N248" s="1" t="s">
+      <c r="N248" t="s">
         <v>1805</v>
       </c>
-      <c r="O248" s="1" t="s">
+      <c r="O248" t="s">
         <v>1806</v>
       </c>
-      <c r="P248" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q248" s="1" t="s">
+      <c r="P248" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q248" t="s">
         <v>1807</v>
       </c>
-      <c r="R248" s="1">
+      <c r="R248">
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B249" s="1" t="s">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>17</v>
+      </c>
+      <c r="B249" t="s">
         <v>1808</v>
       </c>
-      <c r="C249" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D249" s="1" t="s">
+      <c r="C249" t="s">
+        <v>19</v>
+      </c>
+      <c r="D249" t="s">
         <v>1809</v>
       </c>
-      <c r="E249" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F249" s="1" t="s">
+      <c r="E249" t="s">
+        <v>21</v>
+      </c>
+      <c r="F249" t="s">
         <v>970</v>
       </c>
-      <c r="G249" s="1" t="s">
+      <c r="G249" t="s">
         <v>971</v>
       </c>
-      <c r="H249" s="1" t="s">
+      <c r="H249" t="s">
         <v>1572</v>
       </c>
-      <c r="I249" s="1" t="s">
+      <c r="I249" t="s">
         <v>1810</v>
       </c>
-      <c r="J249" s="1" t="s">
+      <c r="J249" t="s">
         <v>1811</v>
       </c>
-      <c r="K249" s="1" t="s">
+      <c r="K249" t="s">
         <v>69</v>
       </c>
-      <c r="L249" s="1">
+      <c r="L249">
         <v>3716</v>
       </c>
-      <c r="M249" s="1" t="s">
+      <c r="M249" t="s">
         <v>1812</v>
       </c>
-      <c r="N249" s="1" t="s">
+      <c r="N249" t="s">
         <v>1813</v>
       </c>
-      <c r="O249" s="1" t="s">
+      <c r="O249" t="s">
         <v>1814</v>
       </c>
-      <c r="P249" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q249" s="1" t="s">
+      <c r="P249" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q249" t="s">
         <v>1815</v>
       </c>
-      <c r="R249" s="1">
+      <c r="R249">
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A250" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B250" s="1" t="s">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>17</v>
+      </c>
+      <c r="B250" t="s">
         <v>1816</v>
       </c>
-      <c r="C250" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D250" s="1" t="s">
+      <c r="C250" t="s">
+        <v>19</v>
+      </c>
+      <c r="D250" t="s">
         <v>1817</v>
       </c>
-      <c r="E250" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F250" s="1" t="s">
+      <c r="E250" t="s">
+        <v>21</v>
+      </c>
+      <c r="F250" t="s">
         <v>970</v>
       </c>
-      <c r="G250" s="1" t="s">
+      <c r="G250" t="s">
         <v>971</v>
       </c>
-      <c r="H250" s="1" t="s">
+      <c r="H250" t="s">
         <v>1465</v>
       </c>
-      <c r="I250" s="1" t="s">
+      <c r="I250" t="s">
         <v>1818</v>
       </c>
-      <c r="J250" s="1" t="s">
+      <c r="J250" t="s">
         <v>1819</v>
       </c>
-      <c r="K250" s="1" t="s">
+      <c r="K250" t="s">
         <v>27</v>
       </c>
-      <c r="L250" s="1">
+      <c r="L250">
         <v>113</v>
       </c>
-      <c r="M250" s="1" t="s">
+      <c r="M250" t="s">
         <v>1693</v>
       </c>
-      <c r="N250" s="1" t="s">
+      <c r="N250" t="s">
         <v>1820</v>
       </c>
-      <c r="O250" s="1" t="s">
+      <c r="O250" t="s">
         <v>1821</v>
       </c>
-      <c r="P250" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q250" s="1" t="s">
+      <c r="P250" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q250" t="s">
         <v>1822</v>
       </c>
-      <c r="R250" s="1">
+      <c r="R250">
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A251" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B251" s="1" t="s">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>17</v>
+      </c>
+      <c r="B251" t="s">
         <v>1823</v>
       </c>
-      <c r="C251" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D251" s="1" t="s">
+      <c r="C251" t="s">
+        <v>19</v>
+      </c>
+      <c r="D251" t="s">
         <v>1824</v>
       </c>
-      <c r="E251" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F251" s="1" t="s">
+      <c r="E251" t="s">
+        <v>21</v>
+      </c>
+      <c r="F251" t="s">
         <v>970</v>
       </c>
-      <c r="G251" s="1" t="s">
+      <c r="G251" t="s">
         <v>971</v>
       </c>
-      <c r="H251" s="1" t="s">
+      <c r="H251" t="s">
         <v>1825</v>
       </c>
-      <c r="I251" s="1" t="s">
+      <c r="I251" t="s">
         <v>1826</v>
       </c>
-      <c r="J251" s="1" t="s">
+      <c r="J251" t="s">
         <v>1827</v>
       </c>
-      <c r="K251" s="1" t="s">
+      <c r="K251" t="s">
         <v>27</v>
       </c>
-      <c r="L251" s="1">
+      <c r="L251">
         <v>230</v>
       </c>
-      <c r="M251" s="1" t="s">
+      <c r="M251" t="s">
         <v>1828</v>
       </c>
-      <c r="N251" s="1" t="s">
+      <c r="N251" t="s">
         <v>1820</v>
       </c>
-      <c r="O251" s="1" t="s">
+      <c r="O251" t="s">
         <v>1829</v>
       </c>
-      <c r="P251" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q251" s="1" t="s">
+      <c r="P251" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q251" t="s">
         <v>1830</v>
       </c>
-      <c r="R251" s="1">
+      <c r="R251">
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A252" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B252" s="1" t="s">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>17</v>
+      </c>
+      <c r="B252" t="s">
         <v>1831</v>
       </c>
-      <c r="C252" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D252" s="1" t="s">
+      <c r="C252" t="s">
+        <v>19</v>
+      </c>
+      <c r="D252" t="s">
         <v>1832</v>
       </c>
-      <c r="E252" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F252" s="1" t="s">
+      <c r="E252" t="s">
+        <v>21</v>
+      </c>
+      <c r="F252" t="s">
         <v>1182</v>
       </c>
-      <c r="G252" s="1" t="s">
+      <c r="G252" t="s">
         <v>1489</v>
       </c>
-      <c r="H252" s="1" t="s">
+      <c r="H252" t="s">
         <v>1034</v>
       </c>
-      <c r="I252" s="1" t="s">
+      <c r="I252" t="s">
         <v>1833</v>
       </c>
-      <c r="J252" s="1" t="s">
+      <c r="J252" t="s">
         <v>1834</v>
       </c>
-      <c r="K252" s="1" t="s">
+      <c r="K252" t="s">
         <v>58</v>
       </c>
-      <c r="L252" s="1">
+      <c r="L252">
         <v>7766</v>
       </c>
-      <c r="M252" s="1" t="s">
+      <c r="M252" t="s">
         <v>1438</v>
       </c>
-      <c r="N252" s="1" t="s">
+      <c r="N252" t="s">
         <v>1835</v>
       </c>
-      <c r="O252" s="1" t="s">
+      <c r="O252" t="s">
         <v>1836</v>
       </c>
-      <c r="P252" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q252" s="1" t="s">
+      <c r="P252" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q252" t="s">
         <v>1837</v>
       </c>
-      <c r="R252" s="1">
+      <c r="R252">
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A253" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B253" s="1" t="s">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>17</v>
+      </c>
+      <c r="B253" t="s">
         <v>1838</v>
       </c>
-      <c r="C253" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D253" s="1" t="s">
+      <c r="C253" t="s">
+        <v>19</v>
+      </c>
+      <c r="D253" t="s">
         <v>1839</v>
       </c>
-      <c r="E253" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F253" s="1" t="s">
+      <c r="E253" t="s">
+        <v>21</v>
+      </c>
+      <c r="F253" t="s">
         <v>970</v>
       </c>
-      <c r="G253" s="1" t="s">
+      <c r="G253" t="s">
         <v>971</v>
       </c>
-      <c r="H253" s="1" t="s">
+      <c r="H253" t="s">
         <v>1840</v>
       </c>
-      <c r="I253" s="1" t="s">
+      <c r="I253" t="s">
         <v>1841</v>
       </c>
-      <c r="J253" s="1" t="s">
+      <c r="J253" t="s">
         <v>1842</v>
       </c>
-      <c r="K253" s="1" t="s">
+      <c r="K253" t="s">
         <v>69</v>
       </c>
-      <c r="L253" s="1">
+      <c r="L253">
         <v>3469</v>
       </c>
-      <c r="M253" s="1" t="s">
+      <c r="M253" t="s">
         <v>1648</v>
       </c>
-      <c r="N253" s="1" t="s">
+      <c r="N253" t="s">
         <v>1843</v>
       </c>
-      <c r="O253" s="1" t="s">
+      <c r="O253" t="s">
         <v>1844</v>
       </c>
-      <c r="P253" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q253" s="1" t="s">
+      <c r="P253" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q253" t="s">
         <v>1845</v>
       </c>
-      <c r="R253" s="1">
+      <c r="R253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>0</v>
+      </c>
+      <c r="B254" t="s">
+        <v>1</v>
+      </c>
+      <c r="C254" t="s">
+        <v>2</v>
+      </c>
+      <c r="D254" t="s">
+        <v>3</v>
+      </c>
+      <c r="E254" t="s">
+        <v>4</v>
+      </c>
+      <c r="F254" t="s">
+        <v>5</v>
+      </c>
+      <c r="G254" t="s">
+        <v>6</v>
+      </c>
+      <c r="H254" t="s">
+        <v>7</v>
+      </c>
+      <c r="I254" t="s">
+        <v>8</v>
+      </c>
+      <c r="J254" t="s">
+        <v>9</v>
+      </c>
+      <c r="K254" t="s">
+        <v>10</v>
+      </c>
+      <c r="L254" t="s">
+        <v>11</v>
+      </c>
+      <c r="M254" t="s">
+        <v>12</v>
+      </c>
+      <c r="N254" t="s">
+        <v>13</v>
+      </c>
+      <c r="O254" t="s">
+        <v>14</v>
+      </c>
+      <c r="P254" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q254" t="s">
+        <v>16</v>
+      </c>
+      <c r="R254" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>17</v>
+      </c>
+      <c r="B255" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C255" t="s">
+        <v>19</v>
+      </c>
+      <c r="D255" t="s">
+        <v>1847</v>
+      </c>
+      <c r="E255" t="s">
+        <v>21</v>
+      </c>
+      <c r="F255" t="s">
+        <v>970</v>
+      </c>
+      <c r="G255" t="s">
+        <v>971</v>
+      </c>
+      <c r="H255" t="s">
+        <v>1689</v>
+      </c>
+      <c r="I255" t="s">
+        <v>1848</v>
+      </c>
+      <c r="J255" t="s">
+        <v>1849</v>
+      </c>
+      <c r="K255" t="s">
+        <v>27</v>
+      </c>
+      <c r="L255">
+        <v>945</v>
+      </c>
+      <c r="M255" t="s">
+        <v>1850</v>
+      </c>
+      <c r="N255" t="s">
+        <v>1851</v>
+      </c>
+      <c r="O255" t="s">
+        <v>1852</v>
+      </c>
+      <c r="P255" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q255" t="s">
+        <v>1853</v>
+      </c>
+      <c r="R255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>17</v>
+      </c>
+      <c r="B256" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C256" t="s">
+        <v>19</v>
+      </c>
+      <c r="D256" t="s">
+        <v>1855</v>
+      </c>
+      <c r="E256" t="s">
+        <v>21</v>
+      </c>
+      <c r="F256" t="s">
+        <v>970</v>
+      </c>
+      <c r="G256" t="s">
+        <v>971</v>
+      </c>
+      <c r="H256" t="s">
+        <v>1564</v>
+      </c>
+      <c r="I256" t="s">
+        <v>1856</v>
+      </c>
+      <c r="J256" t="s">
+        <v>1857</v>
+      </c>
+      <c r="K256" t="s">
+        <v>27</v>
+      </c>
+      <c r="L256">
+        <v>655</v>
+      </c>
+      <c r="M256" t="s">
+        <v>1858</v>
+      </c>
+      <c r="N256" t="s">
+        <v>1851</v>
+      </c>
+      <c r="O256" t="s">
+        <v>1859</v>
+      </c>
+      <c r="P256" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q256" t="s">
+        <v>1860</v>
+      </c>
+      <c r="R256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>17</v>
+      </c>
+      <c r="B257" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C257" t="s">
+        <v>19</v>
+      </c>
+      <c r="D257" t="s">
+        <v>1862</v>
+      </c>
+      <c r="E257" t="s">
+        <v>21</v>
+      </c>
+      <c r="F257" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G257" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H257" t="s">
+        <v>1360</v>
+      </c>
+      <c r="I257" t="s">
+        <v>1863</v>
+      </c>
+      <c r="J257" t="s">
+        <v>1864</v>
+      </c>
+      <c r="K257" t="s">
+        <v>237</v>
+      </c>
+      <c r="L257">
+        <v>11514</v>
+      </c>
+      <c r="M257" t="s">
+        <v>1347</v>
+      </c>
+      <c r="N257" t="s">
+        <v>1865</v>
+      </c>
+      <c r="O257" t="s">
+        <v>1866</v>
+      </c>
+      <c r="P257" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q257" t="s">
+        <v>1867</v>
+      </c>
+      <c r="R257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>17</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C258" t="s">
+        <v>19</v>
+      </c>
+      <c r="D258" t="s">
+        <v>1869</v>
+      </c>
+      <c r="E258" t="s">
+        <v>21</v>
+      </c>
+      <c r="F258" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G258" t="s">
+        <v>1871</v>
+      </c>
+      <c r="H258" t="s">
+        <v>1872</v>
+      </c>
+      <c r="I258" t="s">
+        <v>1873</v>
+      </c>
+      <c r="J258" t="s">
+        <v>1874</v>
+      </c>
+      <c r="K258" t="s">
+        <v>58</v>
+      </c>
+      <c r="L258">
+        <v>7419</v>
+      </c>
+      <c r="M258" t="s">
+        <v>1789</v>
+      </c>
+      <c r="N258" t="s">
+        <v>1875</v>
+      </c>
+      <c r="O258" t="s">
+        <v>1876</v>
+      </c>
+      <c r="P258" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q258" t="s">
+        <v>1877</v>
+      </c>
+      <c r="R258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>17</v>
+      </c>
+      <c r="B259" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C259" t="s">
+        <v>19</v>
+      </c>
+      <c r="D259" t="s">
+        <v>1879</v>
+      </c>
+      <c r="E259" t="s">
+        <v>21</v>
+      </c>
+      <c r="F259" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G259" t="s">
+        <v>1871</v>
+      </c>
+      <c r="H259" t="s">
+        <v>1572</v>
+      </c>
+      <c r="I259" t="s">
+        <v>1880</v>
+      </c>
+      <c r="J259" t="s">
+        <v>1881</v>
+      </c>
+      <c r="K259" t="s">
+        <v>69</v>
+      </c>
+      <c r="L259">
+        <v>1865</v>
+      </c>
+      <c r="M259" t="s">
+        <v>1757</v>
+      </c>
+      <c r="N259" t="s">
+        <v>1882</v>
+      </c>
+      <c r="O259" t="s">
+        <v>1883</v>
+      </c>
+      <c r="P259" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q259" t="s">
+        <v>1884</v>
+      </c>
+      <c r="R259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>17</v>
+      </c>
+      <c r="B260" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C260" t="s">
+        <v>19</v>
+      </c>
+      <c r="D260" t="s">
+        <v>1886</v>
+      </c>
+      <c r="E260" t="s">
+        <v>21</v>
+      </c>
+      <c r="F260" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G260" t="s">
+        <v>1871</v>
+      </c>
+      <c r="H260" t="s">
+        <v>55</v>
+      </c>
+      <c r="I260" t="s">
+        <v>1887</v>
+      </c>
+      <c r="J260" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K260" t="s">
+        <v>69</v>
+      </c>
+      <c r="L260">
+        <v>4528</v>
+      </c>
+      <c r="M260" t="s">
+        <v>1742</v>
+      </c>
+      <c r="N260" t="s">
+        <v>1889</v>
+      </c>
+      <c r="O260" t="s">
+        <v>1890</v>
+      </c>
+      <c r="P260" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q260" t="s">
+        <v>1891</v>
+      </c>
+      <c r="R260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A261" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="F261" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="G261" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="H261" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="I261" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="J261" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="K261" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="L261" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="M261" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="N261" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="O261" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="P261" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="Q261" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="R261" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="S261" s="2" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="262" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F262" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G262" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H262" s="2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="I262" s="2" t="s">
+        <v>1894</v>
+      </c>
+      <c r="J262" s="2" t="s">
+        <v>1895</v>
+      </c>
+      <c r="K262" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L262" s="2">
+        <v>775</v>
+      </c>
+      <c r="M262" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="N262" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="O262" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="P262" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q262" s="2" t="s">
+        <v>1899</v>
+      </c>
+      <c r="R262" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A263" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>1900</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F263" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G263" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H263" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="I263" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="J263" s="2" t="s">
+        <v>1606</v>
+      </c>
+      <c r="K263" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L263" s="2">
+        <v>4772</v>
+      </c>
+      <c r="M263" s="2" t="s">
+        <v>1607</v>
+      </c>
+      <c r="N263" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="O263" s="2" t="s">
+        <v>1902</v>
+      </c>
+      <c r="P263" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q263" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="R263" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A264" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>1904</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F264" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G264" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H264" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="I264" s="2" t="s">
+        <v>1906</v>
+      </c>
+      <c r="J264" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="K264" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L264" s="2">
+        <v>856</v>
+      </c>
+      <c r="M264" s="2" t="s">
+        <v>1805</v>
+      </c>
+      <c r="N264" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="O264" s="2" t="s">
+        <v>1908</v>
+      </c>
+      <c r="P264" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q264" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="R264" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A265" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F265" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G265" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H265" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="I265" s="2" t="s">
+        <v>1913</v>
+      </c>
+      <c r="J265" s="2" t="s">
+        <v>1914</v>
+      </c>
+      <c r="K265" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L265" s="2">
+        <v>495</v>
+      </c>
+      <c r="M265" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="N265" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="O265" s="2" t="s">
+        <v>1915</v>
+      </c>
+      <c r="P265" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q265" s="2" t="s">
+        <v>1916</v>
+      </c>
+      <c r="R265" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A266" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>1918</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F266" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G266" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H266" s="2" t="s">
+        <v>1919</v>
+      </c>
+      <c r="I266" s="2" t="s">
+        <v>1920</v>
+      </c>
+      <c r="J266" s="2" t="s">
+        <v>1921</v>
+      </c>
+      <c r="K266" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L266" s="2">
+        <v>3465</v>
+      </c>
+      <c r="M266" s="2" t="s">
+        <v>1922</v>
+      </c>
+      <c r="N266" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="O266" s="2" t="s">
+        <v>1924</v>
+      </c>
+      <c r="P266" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q266" s="2" t="s">
+        <v>1925</v>
+      </c>
+      <c r="R266" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A267" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>1927</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F267" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G267" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H267" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="I267" s="2" t="s">
+        <v>1928</v>
+      </c>
+      <c r="J267" s="2" t="s">
+        <v>1929</v>
+      </c>
+      <c r="K267" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L267" s="2">
+        <v>424</v>
+      </c>
+      <c r="M267" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="N267" s="2" t="s">
+        <v>1930</v>
+      </c>
+      <c r="O267" s="2" t="s">
+        <v>1931</v>
+      </c>
+      <c r="P267" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q267" s="2" t="s">
+        <v>1932</v>
+      </c>
+      <c r="R267" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A268" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>1934</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F268" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G268" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H268" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="I268" s="2" t="s">
+        <v>1935</v>
+      </c>
+      <c r="J268" s="2" t="s">
+        <v>1936</v>
+      </c>
+      <c r="K268" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L268" s="2">
+        <v>769</v>
+      </c>
+      <c r="M268" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="N268" s="2" t="s">
+        <v>1938</v>
+      </c>
+      <c r="O268" s="2" t="s">
+        <v>1939</v>
+      </c>
+      <c r="P268" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q268" s="2" t="s">
+        <v>1940</v>
+      </c>
+      <c r="R268" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A269" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>1942</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F269" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G269" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H269" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="I269" s="2" t="s">
+        <v>1943</v>
+      </c>
+      <c r="J269" s="2" t="s">
+        <v>1944</v>
+      </c>
+      <c r="K269" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L269" s="2">
+        <v>506</v>
+      </c>
+      <c r="M269" s="2" t="s">
+        <v>1945</v>
+      </c>
+      <c r="N269" s="2" t="s">
+        <v>1938</v>
+      </c>
+      <c r="O269" s="2" t="s">
+        <v>1946</v>
+      </c>
+      <c r="P269" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q269" s="2" t="s">
+        <v>1947</v>
+      </c>
+      <c r="R269" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A270" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F270" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G270" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H270" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="I270" s="2" t="s">
+        <v>1950</v>
+      </c>
+      <c r="J270" s="2" t="s">
+        <v>1951</v>
+      </c>
+      <c r="K270" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L270" s="2">
+        <v>683</v>
+      </c>
+      <c r="M270" s="2" t="s">
+        <v>1952</v>
+      </c>
+      <c r="N270" s="2" t="s">
+        <v>1938</v>
+      </c>
+      <c r="O270" s="2" t="s">
+        <v>1953</v>
+      </c>
+      <c r="P270" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q270" s="2" t="s">
+        <v>1954</v>
+      </c>
+      <c r="R270" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A271" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>1956</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F271" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G271" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H271" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="I271" s="2" t="s">
+        <v>1957</v>
+      </c>
+      <c r="J271" s="2" t="s">
+        <v>1958</v>
+      </c>
+      <c r="K271" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L271" s="2">
+        <v>9656</v>
+      </c>
+      <c r="M271" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="N271" s="2" t="s">
+        <v>1959</v>
+      </c>
+      <c r="O271" s="2" t="s">
+        <v>1960</v>
+      </c>
+      <c r="P271" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q271" s="2" t="s">
+        <v>1961</v>
+      </c>
+      <c r="R271" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A272" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E272" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F272" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G272" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H272" s="2" t="s">
+        <v>1840</v>
+      </c>
+      <c r="I272" s="2" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J272" s="2" t="s">
+        <v>1965</v>
+      </c>
+      <c r="K272" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L272" s="2">
+        <v>425</v>
+      </c>
+      <c r="M272" s="2" t="s">
+        <v>1966</v>
+      </c>
+      <c r="N272" s="2" t="s">
+        <v>1959</v>
+      </c>
+      <c r="O272" s="2" t="s">
+        <v>1967</v>
+      </c>
+      <c r="P272" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q272" s="2" t="s">
+        <v>1968</v>
+      </c>
+      <c r="R272" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A273" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F273" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G273" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H273" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="I273" s="2" t="s">
+        <v>1971</v>
+      </c>
+      <c r="J273" s="2" t="s">
+        <v>1972</v>
+      </c>
+      <c r="K273" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L273" s="2">
+        <v>882</v>
+      </c>
+      <c r="M273" s="2" t="s">
+        <v>1973</v>
+      </c>
+      <c r="N273" s="2" t="s">
+        <v>1974</v>
+      </c>
+      <c r="O273" s="2" t="s">
+        <v>1975</v>
+      </c>
+      <c r="P273" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q273" s="2" t="s">
+        <v>1976</v>
+      </c>
+      <c r="R273" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A274" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>1977</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>1978</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F274" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G274" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H274" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="I274" s="2" t="s">
+        <v>1979</v>
+      </c>
+      <c r="J274" s="2" t="s">
+        <v>1980</v>
+      </c>
+      <c r="K274" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L274" s="2">
+        <v>520</v>
+      </c>
+      <c r="M274" s="2" t="s">
+        <v>1981</v>
+      </c>
+      <c r="N274" s="2" t="s">
+        <v>1974</v>
+      </c>
+      <c r="O274" s="2" t="s">
+        <v>1982</v>
+      </c>
+      <c r="P274" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q274" s="2" t="s">
+        <v>1983</v>
+      </c>
+      <c r="R274" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A275" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>1984</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F275" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G275" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H275" s="2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="I275" s="2" t="s">
+        <v>1986</v>
+      </c>
+      <c r="J275" s="2" t="s">
+        <v>1987</v>
+      </c>
+      <c r="K275" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L275" s="2">
+        <v>965</v>
+      </c>
+      <c r="M275" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="N275" s="2" t="s">
+        <v>1974</v>
+      </c>
+      <c r="O275" s="2" t="s">
+        <v>1988</v>
+      </c>
+      <c r="P275" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q275" s="2" t="s">
+        <v>1989</v>
+      </c>
+      <c r="R275" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A276" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>1990</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F276" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G276" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H276" s="2" t="s">
+        <v>1992</v>
+      </c>
+      <c r="I276" s="2" t="s">
+        <v>1993</v>
+      </c>
+      <c r="J276" s="2" t="s">
+        <v>1994</v>
+      </c>
+      <c r="K276" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L276" s="2">
+        <v>889</v>
+      </c>
+      <c r="M276" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="N276" s="2" t="s">
+        <v>1974</v>
+      </c>
+      <c r="O276" s="2" t="s">
+        <v>1995</v>
+      </c>
+      <c r="P276" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q276" s="2" t="s">
+        <v>1996</v>
+      </c>
+      <c r="R276" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A277" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>1997</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>1998</v>
+      </c>
+      <c r="E277" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F277" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G277" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H277" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="I277" s="2" t="s">
+        <v>1999</v>
+      </c>
+      <c r="J277" s="2" t="s">
+        <v>2000</v>
+      </c>
+      <c r="K277" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L277" s="2">
+        <v>3040</v>
+      </c>
+      <c r="M277" s="2" t="s">
+        <v>2001</v>
+      </c>
+      <c r="N277" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="O277" s="2" t="s">
+        <v>2003</v>
+      </c>
+      <c r="P277" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q277" s="2" t="s">
+        <v>2004</v>
+      </c>
+      <c r="R277" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A278" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>2005</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F278" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G278" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H278" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I278" s="2" t="s">
+        <v>2007</v>
+      </c>
+      <c r="J278" s="2" t="s">
+        <v>2008</v>
+      </c>
+      <c r="K278" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L278" s="2">
+        <v>12</v>
+      </c>
+      <c r="M278" s="2" t="s">
+        <v>2009</v>
+      </c>
+      <c r="N278" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="O278" s="2" t="s">
+        <v>2010</v>
+      </c>
+      <c r="P278" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q278" s="2" t="s">
+        <v>2011</v>
+      </c>
+      <c r="R278" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A279" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>2013</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F279" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G279" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H279" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I279" s="2" t="s">
+        <v>2014</v>
+      </c>
+      <c r="J279" s="2" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K279" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="L279" s="2">
+        <v>5927</v>
+      </c>
+      <c r="M279" s="2" t="s">
+        <v>2016</v>
+      </c>
+      <c r="N279" s="2" t="s">
+        <v>2017</v>
+      </c>
+      <c r="O279" s="2" t="s">
+        <v>2018</v>
+      </c>
+      <c r="P279" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q279" s="2" t="s">
+        <v>2019</v>
+      </c>
+      <c r="R279" s="2">
         <v>0</v>
       </c>
     </row>
@@ -19542,77 +21527,80 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+        <v>977</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>978</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>979</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
+        <v>980</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>981</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
+        <v>982</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>983</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>984</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>985</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>986</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>987</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>988</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>989</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>990</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>991</v>
       </c>
       <c r="P1" t="s">
-        <v>15</v>
+        <v>992</v>
       </c>
       <c r="Q1" t="s">
-        <v>16</v>
+        <v>993</v>
       </c>
       <c r="R1" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+        <v>994</v>
+      </c>
+      <c r="S1" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>1800</v>
+        <v>1892</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>1801</v>
+        <v>1893</v>
       </c>
       <c r="E2" t="s">
         <v>21</v>
@@ -19624,219 +21612,219 @@
         <v>1183</v>
       </c>
       <c r="H2" t="s">
-        <v>1794</v>
+        <v>1572</v>
       </c>
       <c r="I2" t="s">
-        <v>1802</v>
+        <v>1894</v>
       </c>
       <c r="J2" t="s">
-        <v>1803</v>
+        <v>1895</v>
       </c>
       <c r="K2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="L2">
-        <v>3407</v>
+        <v>775</v>
       </c>
       <c r="M2" t="s">
-        <v>1804</v>
+        <v>1896</v>
       </c>
       <c r="N2" t="s">
-        <v>1805</v>
+        <v>1897</v>
       </c>
       <c r="O2" t="s">
-        <v>1806</v>
+        <v>1898</v>
       </c>
       <c r="P2" t="s">
         <v>31</v>
       </c>
       <c r="Q2" t="s">
-        <v>1807</v>
+        <v>1899</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>1808</v>
+        <v>1900</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>1809</v>
+        <v>1901</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>970</v>
+        <v>1182</v>
       </c>
       <c r="G3" t="s">
-        <v>971</v>
+        <v>1183</v>
       </c>
       <c r="H3" t="s">
-        <v>1572</v>
+        <v>1564</v>
       </c>
       <c r="I3" t="s">
-        <v>1810</v>
+        <v>1605</v>
       </c>
       <c r="J3" t="s">
-        <v>1811</v>
+        <v>1606</v>
       </c>
       <c r="K3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="L3">
-        <v>3716</v>
+        <v>4772</v>
       </c>
       <c r="M3" t="s">
-        <v>1812</v>
+        <v>1607</v>
       </c>
       <c r="N3" t="s">
-        <v>1813</v>
+        <v>1897</v>
       </c>
       <c r="O3" t="s">
-        <v>1814</v>
+        <v>1902</v>
       </c>
       <c r="P3" t="s">
         <v>31</v>
       </c>
       <c r="Q3" t="s">
-        <v>1815</v>
+        <v>1609</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>1816</v>
+        <v>1903</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>1817</v>
+        <v>1904</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>970</v>
+        <v>1182</v>
       </c>
       <c r="G4" t="s">
-        <v>971</v>
+        <v>1183</v>
       </c>
       <c r="H4" t="s">
-        <v>1465</v>
+        <v>1905</v>
       </c>
       <c r="I4" t="s">
-        <v>1818</v>
+        <v>1906</v>
       </c>
       <c r="J4" t="s">
-        <v>1819</v>
+        <v>1907</v>
       </c>
       <c r="K4" t="s">
         <v>27</v>
       </c>
       <c r="L4">
-        <v>113</v>
+        <v>856</v>
       </c>
       <c r="M4" t="s">
-        <v>1693</v>
+        <v>1805</v>
       </c>
       <c r="N4" t="s">
-        <v>1820</v>
+        <v>1897</v>
       </c>
       <c r="O4" t="s">
-        <v>1821</v>
+        <v>1908</v>
       </c>
       <c r="P4" t="s">
         <v>31</v>
       </c>
       <c r="Q4" t="s">
-        <v>1822</v>
+        <v>1909</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>1823</v>
+        <v>1910</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>1824</v>
+        <v>1911</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>970</v>
+        <v>1182</v>
       </c>
       <c r="G5" t="s">
-        <v>971</v>
+        <v>1183</v>
       </c>
       <c r="H5" t="s">
-        <v>1825</v>
+        <v>1912</v>
       </c>
       <c r="I5" t="s">
-        <v>1826</v>
+        <v>1913</v>
       </c>
       <c r="J5" t="s">
-        <v>1827</v>
+        <v>1914</v>
       </c>
       <c r="K5" t="s">
         <v>27</v>
       </c>
       <c r="L5">
-        <v>230</v>
+        <v>495</v>
       </c>
       <c r="M5" t="s">
-        <v>1828</v>
+        <v>1835</v>
       </c>
       <c r="N5" t="s">
-        <v>1820</v>
+        <v>1897</v>
       </c>
       <c r="O5" t="s">
-        <v>1829</v>
+        <v>1915</v>
       </c>
       <c r="P5" t="s">
         <v>31</v>
       </c>
       <c r="Q5" t="s">
-        <v>1830</v>
+        <v>1916</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>1831</v>
+        <v>1917</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>1832</v>
+        <v>1918</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
@@ -19845,95 +21833,767 @@
         <v>1182</v>
       </c>
       <c r="G6" t="s">
-        <v>1489</v>
+        <v>1183</v>
       </c>
       <c r="H6" t="s">
-        <v>1034</v>
+        <v>1919</v>
       </c>
       <c r="I6" t="s">
-        <v>1833</v>
+        <v>1920</v>
       </c>
       <c r="J6" t="s">
-        <v>1834</v>
+        <v>1921</v>
       </c>
       <c r="K6" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="L6">
-        <v>7766</v>
+        <v>3465</v>
       </c>
       <c r="M6" t="s">
-        <v>1438</v>
+        <v>1922</v>
       </c>
       <c r="N6" t="s">
-        <v>1835</v>
+        <v>1923</v>
       </c>
       <c r="O6" t="s">
-        <v>1836</v>
+        <v>1924</v>
       </c>
       <c r="P6" t="s">
         <v>31</v>
       </c>
       <c r="Q6" t="s">
-        <v>1837</v>
+        <v>1925</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>1838</v>
+        <v>1926</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>1839</v>
+        <v>1927</v>
       </c>
       <c r="E7" t="s">
         <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>970</v>
+        <v>1182</v>
       </c>
       <c r="G7" t="s">
-        <v>971</v>
+        <v>1183</v>
       </c>
       <c r="H7" t="s">
+        <v>1368</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1928</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1929</v>
+      </c>
+      <c r="K7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7">
+        <v>424</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1835</v>
+      </c>
+      <c r="N7" t="s">
+        <v>1930</v>
+      </c>
+      <c r="O7" t="s">
+        <v>1931</v>
+      </c>
+      <c r="P7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>1932</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1934</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1905</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1935</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1936</v>
+      </c>
+      <c r="K8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8">
+        <v>769</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1937</v>
+      </c>
+      <c r="N8" t="s">
+        <v>1938</v>
+      </c>
+      <c r="O8" t="s">
+        <v>1939</v>
+      </c>
+      <c r="P8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>1940</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1942</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1465</v>
+      </c>
+      <c r="I9" t="s">
+        <v>1943</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1944</v>
+      </c>
+      <c r="K9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9">
+        <v>506</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1945</v>
+      </c>
+      <c r="N9" t="s">
+        <v>1938</v>
+      </c>
+      <c r="O9" t="s">
+        <v>1946</v>
+      </c>
+      <c r="P9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>1947</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1905</v>
+      </c>
+      <c r="I10" t="s">
+        <v>1950</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1951</v>
+      </c>
+      <c r="K10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10">
+        <v>683</v>
+      </c>
+      <c r="M10" t="s">
+        <v>1952</v>
+      </c>
+      <c r="N10" t="s">
+        <v>1938</v>
+      </c>
+      <c r="O10" t="s">
+        <v>1953</v>
+      </c>
+      <c r="P10" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>1954</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1956</v>
+      </c>
+      <c r="E11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H11" t="s">
+        <v>429</v>
+      </c>
+      <c r="I11" t="s">
+        <v>1957</v>
+      </c>
+      <c r="J11" t="s">
+        <v>1958</v>
+      </c>
+      <c r="K11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11">
+        <v>9656</v>
+      </c>
+      <c r="M11" t="s">
+        <v>1530</v>
+      </c>
+      <c r="N11" t="s">
+        <v>1959</v>
+      </c>
+      <c r="O11" t="s">
+        <v>1960</v>
+      </c>
+      <c r="P11" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>1961</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H12" t="s">
         <v>1840</v>
       </c>
-      <c r="I7" t="s">
-        <v>1841</v>
-      </c>
-      <c r="J7" t="s">
-        <v>1842</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="I12" t="s">
+        <v>1964</v>
+      </c>
+      <c r="J12" t="s">
+        <v>1965</v>
+      </c>
+      <c r="K12" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12">
+        <v>425</v>
+      </c>
+      <c r="M12" t="s">
+        <v>1966</v>
+      </c>
+      <c r="N12" t="s">
+        <v>1959</v>
+      </c>
+      <c r="O12" t="s">
+        <v>1967</v>
+      </c>
+      <c r="P12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>1968</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1970</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1794</v>
+      </c>
+      <c r="I13" t="s">
+        <v>1971</v>
+      </c>
+      <c r="J13" t="s">
+        <v>1972</v>
+      </c>
+      <c r="K13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13">
+        <v>882</v>
+      </c>
+      <c r="M13" t="s">
+        <v>1973</v>
+      </c>
+      <c r="N13" t="s">
+        <v>1974</v>
+      </c>
+      <c r="O13" t="s">
+        <v>1975</v>
+      </c>
+      <c r="P13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>1976</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1977</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1978</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1794</v>
+      </c>
+      <c r="I14" t="s">
+        <v>1979</v>
+      </c>
+      <c r="J14" t="s">
+        <v>1980</v>
+      </c>
+      <c r="K14" t="s">
+        <v>27</v>
+      </c>
+      <c r="L14">
+        <v>520</v>
+      </c>
+      <c r="M14" t="s">
+        <v>1981</v>
+      </c>
+      <c r="N14" t="s">
+        <v>1974</v>
+      </c>
+      <c r="O14" t="s">
+        <v>1982</v>
+      </c>
+      <c r="P14" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>1983</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1984</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H15" t="s">
+        <v>1711</v>
+      </c>
+      <c r="I15" t="s">
+        <v>1986</v>
+      </c>
+      <c r="J15" t="s">
+        <v>1987</v>
+      </c>
+      <c r="K15" t="s">
+        <v>27</v>
+      </c>
+      <c r="L15">
+        <v>965</v>
+      </c>
+      <c r="M15" t="s">
+        <v>1843</v>
+      </c>
+      <c r="N15" t="s">
+        <v>1974</v>
+      </c>
+      <c r="O15" t="s">
+        <v>1988</v>
+      </c>
+      <c r="P15" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>1989</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1990</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H16" t="s">
+        <v>1992</v>
+      </c>
+      <c r="I16" t="s">
+        <v>1993</v>
+      </c>
+      <c r="J16" t="s">
+        <v>1994</v>
+      </c>
+      <c r="K16" t="s">
+        <v>27</v>
+      </c>
+      <c r="L16">
+        <v>889</v>
+      </c>
+      <c r="M16" t="s">
+        <v>1937</v>
+      </c>
+      <c r="N16" t="s">
+        <v>1974</v>
+      </c>
+      <c r="O16" t="s">
+        <v>1995</v>
+      </c>
+      <c r="P16" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>1996</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1997</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1998</v>
+      </c>
+      <c r="E17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1564</v>
+      </c>
+      <c r="I17" t="s">
+        <v>1999</v>
+      </c>
+      <c r="J17" t="s">
+        <v>2000</v>
+      </c>
+      <c r="K17" t="s">
         <v>69</v>
       </c>
-      <c r="L7">
-        <v>3469</v>
-      </c>
-      <c r="M7" t="s">
-        <v>1648</v>
-      </c>
-      <c r="N7" t="s">
-        <v>1843</v>
-      </c>
-      <c r="O7" t="s">
-        <v>1844</v>
-      </c>
-      <c r="P7" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>1845</v>
-      </c>
-      <c r="R7">
+      <c r="L17">
+        <v>3040</v>
+      </c>
+      <c r="M17" t="s">
+        <v>2001</v>
+      </c>
+      <c r="N17" t="s">
+        <v>2002</v>
+      </c>
+      <c r="O17" t="s">
+        <v>2003</v>
+      </c>
+      <c r="P17" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>2004</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2005</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E18" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H18" t="s">
+        <v>155</v>
+      </c>
+      <c r="I18" t="s">
+        <v>2007</v>
+      </c>
+      <c r="J18" t="s">
+        <v>2008</v>
+      </c>
+      <c r="K18" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18">
+        <v>12</v>
+      </c>
+      <c r="M18" t="s">
+        <v>2009</v>
+      </c>
+      <c r="N18" t="s">
+        <v>2002</v>
+      </c>
+      <c r="O18" t="s">
+        <v>2010</v>
+      </c>
+      <c r="P18" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>2011</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2013</v>
+      </c>
+      <c r="E19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H19" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" t="s">
+        <v>2014</v>
+      </c>
+      <c r="J19" t="s">
+        <v>2015</v>
+      </c>
+      <c r="K19" t="s">
+        <v>237</v>
+      </c>
+      <c r="L19">
+        <v>5927</v>
+      </c>
+      <c r="M19" t="s">
+        <v>2016</v>
+      </c>
+      <c r="N19" t="s">
+        <v>2017</v>
+      </c>
+      <c r="O19" t="s">
+        <v>2018</v>
+      </c>
+      <c r="P19" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>2019</v>
+      </c>
+      <c r="R19">
         <v>0</v>
       </c>
     </row>
